--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-09-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-09-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6427DCC0-BBB4-4C76-A3C3-DF0212C66417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BAAA2C-C008-4A96-AB7D-F5D71E21DA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tính CK" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
     <sheet name="Tồn sản xuất" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Bảng tính CK'!$A$1:$F$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Bảng tính CK'!$A$1:$F$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Phiếu tính CK'!$A$1:$H$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Tồn sản xuất'!$A$1:$H$31</definedName>
   </definedNames>
@@ -264,7 +264,7 @@
 (Aithings giữ 4 thiết bị kiểm tra) 7 mạch lỗi,</t>
   </si>
   <si>
-    <t>Tồn lô 5</t>
+    <t>Tồn lô 4</t>
   </si>
 </sst>
 </file>
@@ -821,21 +821,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -884,6 +869,30 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="8"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -947,21 +956,71 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -979,65 +1038,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1512,7 +1512,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="6" customWidth="1"/>
@@ -1524,74 +1524,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="85"/>
-      <c r="B1" s="86"/>
-      <c r="C1" s="93" t="s">
+      <c r="A1" s="80"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="85"/>
-      <c r="B2" s="86"/>
-      <c r="C2" s="90" t="s">
+      <c r="A2" s="80"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="92"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="87"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="85"/>
-      <c r="B3" s="86"/>
-      <c r="C3" s="98" t="s">
+      <c r="A3" s="80"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="100"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="95"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="87" t="s">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="89"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="84"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="91" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="97"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="43"/>
       <c r="B6" s="43"/>
       <c r="C6" s="43"/>
       <c r="D6" s="44"/>
-      <c r="E6" s="95" t="str">
+      <c r="E6" s="90" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 09 năm 2026</v>
       </c>
-      <c r="F6" s="95"/>
+      <c r="F6" s="90"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="89"/>
+      <c r="D7" s="89"/>
+      <c r="E7" s="89"/>
       <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1671,91 +1671,86 @@
       <c r="F12" s="24"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24">
-        <v>3</v>
-      </c>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26">
-        <f>SUM(C13*D13)</f>
-        <v>0</v>
-      </c>
+      <c r="A13" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="97"/>
+      <c r="C13" s="28">
+        <f>SUM(C11:C12)</f>
+        <v>246</v>
+      </c>
+      <c r="D13" s="29"/>
+      <c r="E13" s="24"/>
       <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="80" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="81"/>
-      <c r="C14" s="28">
-        <f>SUM(C11:C13)</f>
-        <v>246</v>
-      </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="98" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="98"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="27">
+        <f>SUM(E11:E12)</f>
+        <v>1476000</v>
+      </c>
       <c r="F14" s="24"/>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="82" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="82"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="82"/>
-      <c r="E15" s="27">
-        <f>SUM(E11:E13)</f>
-        <v>1476000</v>
-      </c>
-      <c r="F15" s="24"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="46"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="47"/>
       <c r="E16" s="13"/>
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="47"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="18"/>
+      <c r="A17" s="99" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="99"/>
+      <c r="C17" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="99" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="99"/>
+      <c r="F17" s="62" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="83" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="83"/>
-      <c r="C18" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="83" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="83"/>
-      <c r="F18" s="62" t="s">
-        <v>39</v>
+      <c r="A18" s="100" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="100"/>
+      <c r="C18" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="100" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="100"/>
+      <c r="F18" s="17" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="84" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="84"/>
-      <c r="C19" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="84" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="84"/>
-      <c r="F19" s="17" t="s">
-        <v>7</v>
-      </c>
+      <c r="A19" s="34"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="62"/>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="34"/>
@@ -1774,36 +1769,36 @@
       <c r="F21" s="62"/>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="62"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="63"/>
       <c r="E22" s="60"/>
-      <c r="F22" s="62"/>
+      <c r="F22" s="41"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="41"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="41"/>
-    </row>
-    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="83" t="s">
+      <c r="A23" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="83"/>
-      <c r="C24" s="34" t="s">
+      <c r="B23" s="99"/>
+      <c r="C23" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="83" t="s">
+      <c r="D23" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="83"/>
-      <c r="F24" s="62" t="s">
+      <c r="E23" s="99"/>
+      <c r="F23" s="62" t="s">
         <v>9</v>
       </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
@@ -1822,23 +1817,23 @@
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="10"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D23:E23"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C2:F2"/>
@@ -1847,14 +1842,6 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1887,64 +1874,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="108"/>
-      <c r="B1" s="109"/>
-      <c r="C1" s="110" t="s">
+      <c r="A1" s="111"/>
+      <c r="B1" s="112"/>
+      <c r="C1" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="110"/>
-      <c r="E1" s="110"/>
-      <c r="F1" s="110"/>
-      <c r="G1" s="110"/>
-      <c r="H1" s="110"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="113"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="108"/>
-      <c r="B2" s="109"/>
-      <c r="C2" s="119" t="s">
+      <c r="A2" s="111"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="120"/>
-      <c r="E2" s="120"/>
-      <c r="F2" s="120"/>
-      <c r="G2" s="120"/>
-      <c r="H2" s="121"/>
+      <c r="D2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="123"/>
+      <c r="G2" s="123"/>
+      <c r="H2" s="124"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="108"/>
-      <c r="B3" s="109"/>
-      <c r="C3" s="98" t="s">
+      <c r="A3" s="111"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
-      <c r="H3" s="100"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="95"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="108"/>
-      <c r="B4" s="109"/>
-      <c r="C4" s="87" t="s">
+      <c r="A4" s="111"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="89"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="84"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="111" t="s">
+      <c r="A5" s="114" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="112"/>
-      <c r="C5" s="113"/>
-      <c r="D5" s="113"/>
-      <c r="E5" s="113"/>
-      <c r="F5" s="113"/>
-      <c r="G5" s="113"/>
-      <c r="H5" s="114"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="117"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="48"/>
@@ -1993,12 +1980,12 @@
       <c r="H9" s="35"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="115" t="s">
+      <c r="A10" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="116"/>
+      <c r="B10" s="119"/>
       <c r="C10" s="26">
-        <f>'Bảng tính CK'!E15</f>
+        <f>'Bảng tính CK'!E14</f>
         <v>1476000</v>
       </c>
       <c r="D10" s="66"/>
@@ -2008,10 +1995,10 @@
       <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="101" t="s">
+      <c r="A11" s="104" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="102"/>
+      <c r="B11" s="105"/>
       <c r="C11" s="26">
         <v>3</v>
       </c>
@@ -2022,10 +2009,10 @@
       <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="117" t="s">
+      <c r="A12" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="118"/>
+      <c r="B12" s="121"/>
       <c r="C12" s="24">
         <v>0</v>
       </c>
@@ -2036,10 +2023,10 @@
       <c r="H12" s="35"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="107"/>
+      <c r="B13" s="110"/>
       <c r="C13" s="24">
         <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
         <v>0</v>
@@ -2150,7 +2137,7 @@
         <v>20</v>
       </c>
       <c r="C18" s="25">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="D18" s="57">
         <v>1</v>
@@ -2171,11 +2158,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="103" t="s">
+      <c r="A19" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="104"/>
-      <c r="C19" s="105"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="108"/>
       <c r="D19" s="58">
         <f>SUM(D16:D18)</f>
         <v>3</v>
@@ -2208,11 +2195,11 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="80" t="s">
+      <c r="A21" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="122"/>
-      <c r="C21" s="81"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="97"/>
       <c r="D21" s="19"/>
       <c r="E21" s="27">
         <f>SUM(E16:E18)</f>
@@ -2255,40 +2242,40 @@
       <c r="H23" s="35"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="83" t="s">
+      <c r="A24" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="83"/>
-      <c r="C24" s="83" t="s">
+      <c r="B24" s="99"/>
+      <c r="C24" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="D24" s="83"/>
-      <c r="E24" s="123" t="s">
+      <c r="D24" s="99"/>
+      <c r="E24" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="123"/>
-      <c r="G24" s="83" t="s">
+      <c r="F24" s="102"/>
+      <c r="G24" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="83"/>
+      <c r="H24" s="99"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="84" t="s">
+      <c r="A25" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="84"/>
-      <c r="C25" s="84" t="s">
+      <c r="B25" s="100"/>
+      <c r="C25" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="84"/>
-      <c r="E25" s="124" t="s">
+      <c r="D25" s="100"/>
+      <c r="E25" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="124"/>
-      <c r="G25" s="84" t="s">
+      <c r="F25" s="103"/>
+      <c r="G25" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="84"/>
+      <c r="H25" s="100"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="34"/>
@@ -2331,25 +2318,36 @@
       <c r="H29" s="35"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="83" t="s">
+      <c r="A30" s="99" t="s">
         <v>18</v>
       </c>
-      <c r="B30" s="83"/>
-      <c r="C30" s="83" t="s">
+      <c r="B30" s="99"/>
+      <c r="C30" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="D30" s="83"/>
-      <c r="E30" s="123" t="s">
+      <c r="D30" s="99"/>
+      <c r="E30" s="102" t="s">
         <v>34</v>
       </c>
-      <c r="F30" s="123"/>
-      <c r="G30" s="83" t="s">
+      <c r="F30" s="102"/>
+      <c r="G30" s="99" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="83"/>
+      <c r="H30" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="A30:B30"/>
@@ -2363,17 +2361,6 @@
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
@@ -2403,55 +2390,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="134"/>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="135" t="s">
+      <c r="A1" s="139"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="140" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="141" t="s">
+      <c r="E1" s="141"/>
+      <c r="F1" s="141"/>
+      <c r="G1" s="146" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="142"/>
+      <c r="H1" s="147"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="134"/>
-      <c r="B2" s="134"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="137"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="141" t="s">
+      <c r="A2" s="139"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="146" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="142"/>
+      <c r="H2" s="147"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="134"/>
-      <c r="B3" s="134"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="139"/>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="141" t="s">
+      <c r="A3" s="139"/>
+      <c r="B3" s="139"/>
+      <c r="C3" s="139"/>
+      <c r="D3" s="144"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="146" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="142"/>
+      <c r="H3" s="147"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="133" t="str">
+      <c r="A4" s="138" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 09 năm 2026</v>
       </c>
-      <c r="B4" s="133"/>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="68" t="s">
@@ -2488,27 +2475,27 @@
       <c r="H7" s="69"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="127" t="s">
+      <c r="A8" s="148" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="129" t="s">
+      <c r="C8" s="150" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="131"/>
-      <c r="G8" s="132" t="s">
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="152"/>
+      <c r="G8" s="153" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="132"/>
+      <c r="H8" s="153"/>
       <c r="I8" s="33"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="128"/>
-      <c r="B9" s="128"/>
+      <c r="A9" s="149"/>
+      <c r="B9" s="149"/>
       <c r="C9" s="74" t="s">
         <v>60</v>
       </c>
@@ -2521,8 +2508,8 @@
       <c r="F9" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="132"/>
-      <c r="H9" s="132"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="153"/>
       <c r="I9" s="33"/>
     </row>
     <row r="10" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2609,7 +2596,7 @@
         <v>75</v>
       </c>
       <c r="C13" s="21">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="D13" s="21">
         <v>500</v>
@@ -2647,10 +2634,10 @@
         <f>D14-E14</f>
         <v>2</v>
       </c>
-      <c r="G14" s="146" t="s">
+      <c r="G14" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="146"/>
+      <c r="H14" s="130"/>
       <c r="I14" s="33"/>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2673,10 +2660,10 @@
         <f t="shared" ref="F15" si="0">D15</f>
         <v>178</v>
       </c>
-      <c r="G15" s="146" t="s">
+      <c r="G15" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="146"/>
+      <c r="H15" s="130"/>
       <c r="I15" s="33"/>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2699,10 +2686,10 @@
         <f>D16-E16</f>
         <v>52</v>
       </c>
-      <c r="G16" s="146" t="s">
+      <c r="G16" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="146"/>
+      <c r="H16" s="130"/>
     </row>
     <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="55">
@@ -2724,10 +2711,10 @@
         <f>D17-E17</f>
         <v>22</v>
       </c>
-      <c r="G17" s="146" t="s">
+      <c r="G17" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H17" s="146"/>
+      <c r="H17" s="130"/>
     </row>
     <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="55">
@@ -2749,10 +2736,10 @@
         <f>D18-E18</f>
         <v>2</v>
       </c>
-      <c r="G18" s="146" t="s">
+      <c r="G18" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H18" s="146"/>
+      <c r="H18" s="130"/>
     </row>
     <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="55">
@@ -2773,10 +2760,10 @@
       <c r="F19" s="23">
         <v>3</v>
       </c>
-      <c r="G19" s="146" t="s">
+      <c r="G19" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="H19" s="146"/>
+      <c r="H19" s="130"/>
     </row>
     <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="55">
@@ -2786,18 +2773,20 @@
         <v>66</v>
       </c>
       <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
+      <c r="D20" s="21">
+        <v>68</v>
+      </c>
       <c r="E20" s="21">
         <v>10</v>
       </c>
       <c r="F20" s="23">
         <f>SUM(D20-E20)</f>
-        <v>-10</v>
-      </c>
-      <c r="G20" s="147" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" s="136" t="s">
         <v>68</v>
       </c>
-      <c r="H20" s="148"/>
+      <c r="H20" s="137"/>
     </row>
     <row r="21" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="55">
@@ -2819,23 +2808,23 @@
         <f>SUM(D21-E21)</f>
         <v>1</v>
       </c>
-      <c r="G21" s="145" t="s">
+      <c r="G21" s="135" t="s">
         <v>76</v>
       </c>
-      <c r="H21" s="145"/>
+      <c r="H21" s="135"/>
     </row>
     <row r="22" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="152" t="s">
+      <c r="A22" s="131" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="153"/>
+      <c r="B22" s="132"/>
       <c r="C22" s="56">
         <f>SUM(C10:C21)</f>
-        <v>6960</v>
+        <v>7160</v>
       </c>
       <c r="D22" s="56">
         <f>SUM(D10:D21)</f>
-        <v>3509</v>
+        <v>3577</v>
       </c>
       <c r="E22" s="56">
         <f>SUM(E10:E21)</f>
@@ -2843,10 +2832,10 @@
       </c>
       <c r="F22" s="56">
         <f>SUM(F10:F21)</f>
-        <v>3263</v>
-      </c>
-      <c r="G22" s="143"/>
-      <c r="H22" s="144"/>
+        <v>3331</v>
+      </c>
+      <c r="G22" s="133"/>
+      <c r="H22" s="134"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="69"/>
@@ -2859,40 +2848,40 @@
       <c r="H23" s="69"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="151" t="s">
+      <c r="A24" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="151"/>
-      <c r="C24" s="151" t="s">
+      <c r="B24" s="129"/>
+      <c r="C24" s="129" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="151"/>
-      <c r="E24" s="151" t="s">
+      <c r="D24" s="129"/>
+      <c r="E24" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="151"/>
-      <c r="G24" s="83" t="s">
+      <c r="F24" s="129"/>
+      <c r="G24" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="H24" s="83"/>
+      <c r="H24" s="99"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="150" t="s">
+      <c r="A25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="150"/>
-      <c r="C25" s="150" t="s">
+      <c r="B25" s="128"/>
+      <c r="C25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="150"/>
-      <c r="E25" s="150" t="s">
+      <c r="D25" s="128"/>
+      <c r="E25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="F25" s="150"/>
-      <c r="G25" s="150" t="s">
+      <c r="F25" s="128"/>
+      <c r="G25" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="150"/>
+      <c r="H25" s="128"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="75"/>
@@ -2935,22 +2924,22 @@
       <c r="H29" s="77"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="149" t="s">
+      <c r="A30" s="127" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="149"/>
-      <c r="C30" s="149" t="s">
+      <c r="B30" s="127"/>
+      <c r="C30" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="149"/>
-      <c r="E30" s="149" t="s">
+      <c r="D30" s="127"/>
+      <c r="E30" s="127" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="149"/>
-      <c r="G30" s="149" t="s">
+      <c r="F30" s="127"/>
+      <c r="G30" s="127" t="s">
         <v>9</v>
       </c>
-      <c r="H30" s="149"/>
+      <c r="H30" s="127"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="69"/>
@@ -2964,6 +2953,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
@@ -2980,26 +2989,6 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-09-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-09-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BAAA2C-C008-4A96-AB7D-F5D71E21DA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274864CB-BB57-4719-823D-A75607F1C850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tính CK" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Bảng tính CK'!$A$1:$F$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Phiếu tính CK'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Phiếu tính CK'!$A$1:$H$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Tồn sản xuất'!$A$1:$H$31</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="78">
   <si>
     <t>STT</t>
   </si>
@@ -31,9 +31,6 @@
   </si>
   <si>
     <t>Tổng tiền chiết khấu cho cả bộ phận</t>
-  </si>
-  <si>
-    <t>Thêm dòng cho nhân viên mới từ cột này</t>
   </si>
   <si>
     <t>Số nhân viên nghỉ từ 7 ngày/tháng</t>
@@ -218,9 +215,6 @@
     <t>Card Reader (new version)</t>
   </si>
   <si>
-    <t>Tồn lô 1/2026</t>
-  </si>
-  <si>
     <t>VNSH03</t>
   </si>
   <si>
@@ -260,22 +254,24 @@
 1 thiết bị giữ lại để test</t>
   </si>
   <si>
+    <t>Tồn lô 1/2026, 1 PCB lỗi</t>
+  </si>
+  <si>
+    <t>Tồn lô 4/2026</t>
+  </si>
+  <si>
     <t>Đã nhận tổng thực tế 957 mạch, 
-(Aithings giữ 4 thiết bị kiểm tra) 7 mạch lỗi,</t>
-  </si>
-  <si>
-    <t>Tồn lô 4</t>
+(Aithings giữ 4 thiết bị kiểm tra), 7 mạch lỗi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0;[Red]#,##0.0"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -416,19 +412,18 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="15">
@@ -602,7 +597,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -677,15 +672,6 @@
     <xf numFmtId="4" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -734,9 +720,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -821,6 +804,21 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -869,19 +867,67 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -893,75 +939,78 @@
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="7"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -971,74 +1020,8 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bình thường 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1524,91 +1507,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="80"/>
-      <c r="B1" s="81"/>
-      <c r="C1" s="88" t="s">
+      <c r="A1" s="81"/>
+      <c r="B1" s="82"/>
+      <c r="C1" s="89" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="81"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="86" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="87"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="88"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="81"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="94" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="96"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="85" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="86"/>
-      <c r="E2" s="86"/>
-      <c r="F2" s="87"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="93" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="95"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="82" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="85"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="91" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="92"/>
-      <c r="D5" s="92"/>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
+      <c r="A5" s="92" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="92"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="90" t="str">
+      <c r="A6" s="40"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="91" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 09 năm 2026</v>
       </c>
-      <c r="F6" s="90"/>
+      <c r="F6" s="91"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="89" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="89"/>
-      <c r="C7" s="89"/>
-      <c r="D7" s="89"/>
-      <c r="E7" s="89"/>
+      <c r="A7" s="90" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="90"/>
+      <c r="C7" s="90"/>
+      <c r="D7" s="90"/>
+      <c r="E7" s="90"/>
       <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="51"/>
+      <c r="A8" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="47"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="47"/>
       <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
-      <c r="D9" s="45"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="16"/>
       <c r="F9" s="18"/>
     </row>
@@ -1617,19 +1600,19 @@
         <v>0</v>
       </c>
       <c r="B10" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="D10" s="57" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="61" t="s">
+      <c r="F10" s="28" t="s">
         <v>45</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1637,7 +1620,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" s="24">
         <v>236</v>
@@ -1656,7 +1639,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C12" s="24">
         <v>10</v>
@@ -1671,10 +1654,10 @@
       <c r="F12" s="24"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="96" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="97"/>
+      <c r="A13" s="76" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="77"/>
       <c r="C13" s="28">
         <f>SUM(C11:C12)</f>
         <v>246</v>
@@ -1684,12 +1667,12 @@
       <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="98" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="98"/>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
+      <c r="A14" s="78" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="78"/>
+      <c r="C14" s="78"/>
+      <c r="D14" s="78"/>
       <c r="E14" s="27">
         <f>SUM(E11:E12)</f>
         <v>1476000</v>
@@ -1700,7 +1683,7 @@
       <c r="A15" s="13"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
-      <c r="D15" s="46"/>
+      <c r="D15" s="43"/>
       <c r="E15" s="13"/>
       <c r="F15" s="18"/>
     </row>
@@ -1708,88 +1691,88 @@
       <c r="A16" s="13"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
-      <c r="D16" s="47"/>
+      <c r="D16" s="44"/>
       <c r="E16" s="13"/>
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="99" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="99"/>
-      <c r="C17" s="34" t="s">
+      <c r="A17" s="79" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="99" t="s">
+      <c r="B17" s="79"/>
+      <c r="C17" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="79" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="79"/>
+      <c r="F17" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="99"/>
-      <c r="F17" s="62" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="100" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" s="100"/>
+      <c r="A18" s="80" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="80"/>
       <c r="C18" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="100" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="100"/>
+        <v>6</v>
+      </c>
+      <c r="D18" s="80" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="80"/>
       <c r="F18" s="17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="34"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="62"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="62"/>
+      <c r="A19" s="31"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="58"/>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="62"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="62"/>
+      <c r="A20" s="31"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="58"/>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="60"/>
-      <c r="F21" s="62"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="58"/>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="41"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="41"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="56"/>
+      <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="99" t="s">
-        <v>18</v>
-      </c>
-      <c r="B23" s="99"/>
-      <c r="C23" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="99" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="99"/>
-      <c r="F23" s="62" t="s">
-        <v>9</v>
+      <c r="A23" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="79"/>
+      <c r="C23" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="79" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="79"/>
+      <c r="F23" s="58" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1826,6 +1809,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A17:B17"/>
@@ -1834,14 +1825,6 @@
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="C3:F3"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1854,7 +1837,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1874,203 +1857,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="111"/>
-      <c r="B1" s="112"/>
-      <c r="C1" s="113" t="s">
+      <c r="A1" s="104"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="106" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="104"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="115" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="117"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="104"/>
+      <c r="B3" s="105"/>
+      <c r="C3" s="94" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="96"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="104"/>
+      <c r="B4" s="105"/>
+      <c r="C4" s="83" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="111"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="122" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="124"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="111"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="93" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="95"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="111"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="82" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="85"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="114" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="115"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="117"/>
+      <c r="A5" s="107" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="108"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="110"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="48"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36" t="s">
-        <v>71</v>
+      <c r="A6" s="45"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="35"/>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="35"/>
+      <c r="A7" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
     </row>
     <row r="8" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
+      <c r="A8" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
     </row>
     <row r="9" spans="1:8" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="65"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="118" t="s">
+      <c r="A10" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="119"/>
+      <c r="B10" s="112"/>
       <c r="C10" s="26">
         <f>'Bảng tính CK'!E14</f>
         <v>1476000</v>
       </c>
-      <c r="D10" s="66"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="104" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="105"/>
+      <c r="A11" s="97" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="98"/>
       <c r="C11" s="26">
         <v>3</v>
       </c>
-      <c r="D11" s="66"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="120" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="121"/>
+      <c r="A12" s="113" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="114"/>
       <c r="C12" s="24">
         <v>0</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="109" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="110"/>
+      <c r="A13" s="102" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="103"/>
       <c r="C13" s="24">
-        <f>COUNTIFS(C16:C20, "&gt;=2.5",C16:C20,"&lt;7")</f>
+        <f>COUNTIFS(C16:C19, "&gt;=2.5",C16:C19,"&lt;7")</f>
         <v>0</v>
       </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
     </row>
     <row r="14" spans="1:8" s="3" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="35"/>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
     </row>
     <row r="15" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B15" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="D15" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="67" t="s">
+      <c r="E15" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="67" t="s">
+      <c r="F15" s="63" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="67" t="s">
+      <c r="G15" s="63" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="67" t="s">
+      <c r="H15" s="63" t="s">
         <v>56</v>
-      </c>
-      <c r="H15" s="67" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2078,12 +2061,12 @@
         <v>1</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="25">
         <v>2</v>
       </c>
-      <c r="D16" s="57">
+      <c r="D16" s="53">
         <v>1</v>
       </c>
       <c r="E16" s="26">
@@ -2097,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="H16" s="26">
-        <f>((E16-F16)+($F$21/10))-G16</f>
+        <f>((E16-F16)+($F$20/10))-G16</f>
         <v>492000</v>
       </c>
     </row>
@@ -2106,12 +2089,12 @@
         <v>2</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" s="25">
         <v>1</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="53">
         <v>1</v>
       </c>
       <c r="E17" s="26">
@@ -2125,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="26">
-        <f>((E17-F17)+($F$21/10))-G17</f>
+        <f>((E17-F17)+($F$20/10))-G17</f>
         <v>492000</v>
       </c>
     </row>
@@ -2134,12 +2117,12 @@
         <v>3</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="25">
         <v>1.5</v>
       </c>
-      <c r="D18" s="57">
+      <c r="D18" s="53">
         <v>1</v>
       </c>
       <c r="E18" s="26">
@@ -2153,17 +2136,17 @@
         <v>0</v>
       </c>
       <c r="H18" s="26">
-        <f>((E18-F18)+($F$21/10))-G18</f>
+        <f>((E18-F18)+($F$20/10))-G18</f>
         <v>492000</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="106" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="107"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="58">
+      <c r="A19" s="99" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="100"/>
+      <c r="C19" s="101"/>
+      <c r="D19" s="54">
         <f>SUM(D16:D18)</f>
         <v>3</v>
       </c>
@@ -2173,172 +2156,163 @@
       <c r="H19" s="26"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32">
-        <f>IF(OR(C20&gt;=7,C20 =""),0,$C$10/($C$11-$C$12))</f>
-        <v>0</v>
-      </c>
-      <c r="F20" s="32">
-        <f>IF(C20&lt;2.5,0,IF(AND(C20&gt;=2.5,C20&lt;7),(C20-2)*(($C$10/($C$11-$C$12))/7),0))</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32">
-        <f>IF(AND(C20&lt;=2.5,C20&lt;&gt;""),E20+$F$21/($C$11-$C$13-$C$12),E20-F20)</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="50" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="96" t="s">
+      <c r="A20" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="101"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="27">
+      <c r="B20" s="118"/>
+      <c r="C20" s="77"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="27">
         <f>SUM(E16:E18)</f>
         <v>1476000</v>
       </c>
-      <c r="F21" s="27">
-        <f>SUM(F16:F20)</f>
+      <c r="F20" s="27">
+        <f>SUM(F16:F19)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="27">
+      <c r="G20" s="27">
         <f>SUM(G16:G18)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H20" s="27">
         <f>SUM(H16:H18)</f>
         <v>1476000</v>
       </c>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="49" t="s">
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="32"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="79" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="79"/>
+      <c r="E23" s="119" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="119"/>
+      <c r="G23" s="79" t="s">
+        <v>38</v>
+      </c>
+      <c r="H23" s="79"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="80" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="80"/>
+      <c r="C24" s="80" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="80"/>
+      <c r="E24" s="120" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="120"/>
+      <c r="G24" s="80" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="80"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="31"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="49"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="31"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="31"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="38"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="79" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="79"/>
+      <c r="C29" s="79" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="79"/>
+      <c r="E29" s="119" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="119"/>
+      <c r="G29" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="35"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="35"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="35"/>
-      <c r="E23" s="35"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="99" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="99"/>
-      <c r="C24" s="99" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="99"/>
-      <c r="E24" s="102" t="s">
-        <v>38</v>
-      </c>
-      <c r="F24" s="102"/>
-      <c r="G24" s="99" t="s">
-        <v>39</v>
-      </c>
-      <c r="H24" s="99"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="100" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="100"/>
-      <c r="C25" s="100" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="100"/>
-      <c r="E25" s="103" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="103"/>
-      <c r="G25" s="100" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" s="100"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="34"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="53"/>
-      <c r="F26" s="53"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="34"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="35"/>
-      <c r="D27" s="35"/>
-      <c r="E27" s="53"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="35"/>
-      <c r="D28" s="35"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="41"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="99" t="s">
-        <v>18</v>
-      </c>
-      <c r="B30" s="99"/>
-      <c r="C30" s="99" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30" s="99"/>
-      <c r="E30" s="102" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="102"/>
-      <c r="G30" s="99" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="99"/>
+      <c r="H29" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="C1:H1"/>
@@ -2348,22 +2322,9 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C2:H2"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="88" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="91" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="8" max="1048575" man="1"/>
   </colBreaks>
@@ -2390,134 +2351,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="139"/>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="140" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="141"/>
-      <c r="F1" s="141"/>
-      <c r="G1" s="146" t="s">
+      <c r="A1" s="130"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="131" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="148" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="149"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="130"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="134"/>
+      <c r="F2" s="134"/>
+      <c r="G2" s="148" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="147"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="139"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="146" t="s">
+      <c r="H2" s="149"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="130"/>
+      <c r="B3" s="130"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="135"/>
+      <c r="E3" s="136"/>
+      <c r="F3" s="136"/>
+      <c r="G3" s="148" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="147"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="139"/>
-      <c r="B3" s="139"/>
-      <c r="C3" s="139"/>
-      <c r="D3" s="144"/>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="146" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="147"/>
+      <c r="H3" s="149"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="138" t="str">
+      <c r="A4" s="129" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 09 năm 2026</v>
       </c>
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
+      <c r="B4" s="129"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="129"/>
+      <c r="E4" s="129"/>
+      <c r="F4" s="129"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="129"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="65"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="66"/>
+      <c r="H5" s="68"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="72"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="68" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="69"/>
-      <c r="C6" s="69"/>
-      <c r="D6" s="72"/>
-      <c r="E6" s="69"/>
-      <c r="F6" s="73"/>
-      <c r="G6" s="69"/>
-      <c r="H6" s="72"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="68"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="69"/>
-      <c r="B7" s="69"/>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="69"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="H7" s="69"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="65"/>
+      <c r="F7" s="65"/>
+      <c r="G7" s="65"/>
+      <c r="H7" s="65"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="148" t="s">
+      <c r="A8" s="123" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="148" t="s">
+      <c r="B8" s="123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="125" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="150" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="151"/>
-      <c r="E8" s="151"/>
-      <c r="F8" s="152"/>
-      <c r="G8" s="153" t="s">
-        <v>46</v>
-      </c>
-      <c r="H8" s="153"/>
-      <c r="I8" s="33"/>
+      <c r="D8" s="126"/>
+      <c r="E8" s="126"/>
+      <c r="F8" s="127"/>
+      <c r="G8" s="128" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="128"/>
+      <c r="I8" s="30"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="149"/>
-      <c r="B9" s="149"/>
-      <c r="C9" s="74" t="s">
+      <c r="A9" s="124"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="74" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="153"/>
-      <c r="H9" s="153"/>
-      <c r="I9" s="33"/>
-    </row>
-    <row r="10" spans="1:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="55">
+      <c r="G9" s="128"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="30"/>
+    </row>
+    <row r="10" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="51">
         <v>1</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C10" s="21">
         <v>1000</v>
@@ -2532,18 +2493,18 @@
         <f>D10-E10</f>
         <v>2</v>
       </c>
-      <c r="G10" s="125" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="126"/>
-      <c r="I10" s="33"/>
-    </row>
-    <row r="11" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="55">
+      <c r="G10" s="121" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="122"/>
+      <c r="I10" s="30"/>
+    </row>
+    <row r="11" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="51">
         <v>2</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" s="21">
         <v>1000</v>
@@ -2558,18 +2519,18 @@
         <f>SUM(D11-E11)</f>
         <v>11</v>
       </c>
-      <c r="G11" s="125" t="s">
+      <c r="G11" s="121" t="s">
         <v>77</v>
       </c>
-      <c r="H11" s="126"/>
-      <c r="I11" s="33"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="55">
+      <c r="H11" s="122"/>
+      <c r="I11" s="30"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="51">
         <v>5</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="21">
         <v>3000</v>
@@ -2584,16 +2545,16 @@
         <f>SUM(D12-E12)</f>
         <v>2500</v>
       </c>
-      <c r="G12" s="125" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" s="126"/>
-      <c r="I12" s="33"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="55"/>
+      <c r="G12" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="122"/>
+      <c r="I12" s="30"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="51"/>
       <c r="B13" s="20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C13" s="21">
         <v>700</v>
@@ -2608,18 +2569,18 @@
         <f>SUM(D13-E13)</f>
         <v>500</v>
       </c>
-      <c r="G13" s="125" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="126"/>
-      <c r="I13" s="33"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="55">
+      <c r="G13" s="121" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="122"/>
+      <c r="I13" s="30"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="51">
         <v>6</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="21">
         <v>200</v>
@@ -2634,18 +2595,18 @@
         <f>D14-E14</f>
         <v>2</v>
       </c>
-      <c r="G14" s="130" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="130"/>
-      <c r="I14" s="33"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="55">
+      <c r="G14" s="142" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="142"/>
+      <c r="I14" s="30"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="51">
         <v>7</v>
       </c>
-      <c r="B15" s="54" t="s">
-        <v>16</v>
+      <c r="B15" s="50" t="s">
+        <v>15</v>
       </c>
       <c r="C15" s="21">
         <v>200</v>
@@ -2660,18 +2621,18 @@
         <f t="shared" ref="F15" si="0">D15</f>
         <v>178</v>
       </c>
-      <c r="G15" s="130" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="130"/>
-      <c r="I15" s="33"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="55">
+      <c r="G15" s="142" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="142"/>
+      <c r="I15" s="30"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="51">
         <v>8</v>
       </c>
-      <c r="B16" s="54" t="s">
-        <v>15</v>
+      <c r="B16" s="50" t="s">
+        <v>14</v>
       </c>
       <c r="C16" s="21">
         <v>300</v>
@@ -2686,17 +2647,17 @@
         <f>D16-E16</f>
         <v>52</v>
       </c>
-      <c r="G16" s="130" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="130"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55">
+      <c r="G16" s="142" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="142"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="51">
         <v>9</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="21">
         <v>200</v>
@@ -2711,17 +2672,17 @@
         <f>D17-E17</f>
         <v>22</v>
       </c>
-      <c r="G17" s="130" t="s">
-        <v>19</v>
-      </c>
-      <c r="H17" s="130"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="55">
+      <c r="G17" s="142" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" s="142"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="51">
         <v>10</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" s="21">
         <v>30</v>
@@ -2736,17 +2697,17 @@
         <f>D18-E18</f>
         <v>2</v>
       </c>
-      <c r="G18" s="130" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="130"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="55">
+      <c r="G18" s="142" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="142"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="51">
         <v>11</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="21">
         <v>30</v>
@@ -2760,17 +2721,17 @@
       <c r="F19" s="23">
         <v>3</v>
       </c>
-      <c r="G19" s="130" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="130"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="55">
+      <c r="G19" s="142" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="142"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="51">
         <v>12</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C20" s="21"/>
       <c r="D20" s="21">
@@ -2783,17 +2744,17 @@
         <f>SUM(D20-E20)</f>
         <v>58</v>
       </c>
-      <c r="G20" s="136" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" s="137"/>
-    </row>
-    <row r="21" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="55">
+      <c r="G20" s="143" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="144"/>
+    </row>
+    <row r="21" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="51">
         <v>13</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C21" s="21">
         <v>500</v>
@@ -2808,171 +2769,151 @@
         <f>SUM(D21-E21)</f>
         <v>1</v>
       </c>
-      <c r="G21" s="135" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="135"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="131" t="s">
-        <v>17</v>
-      </c>
-      <c r="B22" s="132"/>
-      <c r="C22" s="56">
+      <c r="G21" s="141" t="s">
+        <v>74</v>
+      </c>
+      <c r="H21" s="141"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="137" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="138"/>
+      <c r="C22" s="52">
         <f>SUM(C10:C21)</f>
         <v>7160</v>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="52">
         <f>SUM(D10:D21)</f>
         <v>3577</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E22" s="52">
         <f>SUM(E10:E21)</f>
         <v>246</v>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="52">
         <f>SUM(F10:F21)</f>
         <v>3331</v>
       </c>
-      <c r="G22" s="133"/>
-      <c r="H22" s="134"/>
+      <c r="G22" s="139"/>
+      <c r="H22" s="140"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="69"/>
-      <c r="B23" s="69"/>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
+      <c r="A23" s="65"/>
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="129" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="129"/>
-      <c r="C24" s="129" t="s">
+      <c r="A24" s="147" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="147"/>
+      <c r="C24" s="147" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="147"/>
+      <c r="E24" s="147" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="147"/>
+      <c r="G24" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="129"/>
-      <c r="E24" s="129" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="129"/>
-      <c r="G24" s="99" t="s">
-        <v>39</v>
-      </c>
-      <c r="H24" s="99"/>
+      <c r="H24" s="79"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="128" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25" s="128"/>
-      <c r="C25" s="128" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="128"/>
-      <c r="E25" s="128" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="128"/>
-      <c r="G25" s="128" t="s">
-        <v>7</v>
-      </c>
-      <c r="H25" s="128"/>
+      <c r="A25" s="146" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="146"/>
+      <c r="C25" s="146" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="146"/>
+      <c r="E25" s="146" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="146"/>
+      <c r="G25" s="146" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="146"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="75"/>
-      <c r="B26" s="75"/>
-      <c r="C26" s="75"/>
-      <c r="D26" s="75"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="75"/>
-      <c r="H26" s="75"/>
+      <c r="A26" s="71"/>
+      <c r="B26" s="71"/>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="75"/>
-      <c r="B27" s="75"/>
-      <c r="C27" s="75"/>
-      <c r="D27" s="59"/>
-      <c r="E27" s="75"/>
-      <c r="F27" s="75"/>
-      <c r="G27" s="75"/>
-      <c r="H27" s="75"/>
+      <c r="A27" s="71"/>
+      <c r="B27" s="71"/>
+      <c r="C27" s="71"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="71"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="77"/>
-      <c r="B28" s="77"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="78"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
+      <c r="A28" s="73"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="73"/>
+      <c r="D28" s="73"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="77"/>
-      <c r="B29" s="77"/>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
+      <c r="A29" s="73"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="73"/>
+      <c r="D29" s="73"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="127" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="127"/>
-      <c r="C30" s="127" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="127"/>
-      <c r="E30" s="127" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="127"/>
-      <c r="G30" s="127" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="127"/>
+      <c r="A30" s="145" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="145"/>
+      <c r="C30" s="145" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="145"/>
+      <c r="E30" s="145" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="145"/>
+      <c r="G30" s="145" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="145"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="69"/>
-      <c r="B31" s="69"/>
-      <c r="C31" s="69"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="69"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
+      <c r="A31" s="65"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="65"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H9"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
@@ -2989,6 +2930,26 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="G14:H14"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-09-2026.xlsx
+++ b/5. Other/Chiết khấu/Năm 2026/Chiết-khấu-tháng-09-2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{274864CB-BB57-4719-823D-A75607F1C850}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C6B8EF-1269-4EE8-B5C3-7D41915BC36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng tính CK" sheetId="1" r:id="rId1"/>
@@ -804,21 +804,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -867,6 +852,39 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="8"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -874,15 +892,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -930,21 +939,71 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="8"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -963,65 +1022,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Bình thường 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1507,74 +1507,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="81"/>
-      <c r="B1" s="82"/>
-      <c r="C1" s="89" t="s">
+      <c r="A1" s="76"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="81"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="86" t="s">
+      <c r="A2" s="76"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="88"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="83"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="81"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="94" t="s">
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="96"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="91"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="83" t="s">
+      <c r="A4" s="76"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="85"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="80"/>
     </row>
     <row r="5" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="87" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="40"/>
       <c r="B6" s="40"/>
       <c r="C6" s="40"/>
       <c r="D6" s="41"/>
-      <c r="E6" s="91" t="str">
+      <c r="E6" s="86" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 09 năm 2026</v>
       </c>
-      <c r="F6" s="91"/>
+      <c r="F6" s="86"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="90"/>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
       <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1654,10 +1654,10 @@
       <c r="F12" s="24"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="77"/>
+      <c r="B13" s="93"/>
       <c r="C13" s="28">
         <f>SUM(C11:C12)</f>
         <v>246</v>
@@ -1667,12 +1667,12 @@
       <c r="F13" s="24"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="94" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="78"/>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
       <c r="E14" s="27">
         <f>SUM(E11:E12)</f>
         <v>1476000</v>
@@ -1696,33 +1696,33 @@
       <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="79" t="s">
+      <c r="A17" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="79"/>
+      <c r="B17" s="95"/>
       <c r="C17" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="79" t="s">
+      <c r="D17" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="79"/>
+      <c r="E17" s="95"/>
       <c r="F17" s="58" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="80" t="s">
+      <c r="A18" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="80"/>
+      <c r="B18" s="96"/>
       <c r="C18" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D18" s="80" t="s">
+      <c r="D18" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="80"/>
+      <c r="E18" s="96"/>
       <c r="F18" s="17" t="s">
         <v>6</v>
       </c>
@@ -1760,17 +1760,17 @@
       <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="79" t="s">
+      <c r="A23" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="79"/>
+      <c r="B23" s="95"/>
       <c r="C23" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="79" t="s">
+      <c r="D23" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="79"/>
+      <c r="E23" s="95"/>
       <c r="F23" s="58" t="s">
         <v>8</v>
       </c>
@@ -1809,6 +1809,14 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="D23:E23"/>
     <mergeCell ref="A1:B4"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="C2:F2"/>
@@ -1817,14 +1825,6 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="C3:F3"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="D23:E23"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -1857,64 +1857,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="104"/>
-      <c r="B1" s="105"/>
-      <c r="C1" s="106" t="s">
+      <c r="A1" s="107"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="104"/>
-      <c r="B2" s="105"/>
-      <c r="C2" s="115" t="s">
+      <c r="A2" s="107"/>
+      <c r="B2" s="108"/>
+      <c r="C2" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="117"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="120"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="104"/>
-      <c r="B3" s="105"/>
-      <c r="C3" s="94" t="s">
+      <c r="A3" s="107"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="89" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="95"/>
-      <c r="E3" s="95"/>
-      <c r="F3" s="95"/>
-      <c r="G3" s="95"/>
-      <c r="H3" s="96"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="91"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="104"/>
-      <c r="B4" s="105"/>
-      <c r="C4" s="83" t="s">
+      <c r="A4" s="107"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="85"/>
+      <c r="D4" s="79"/>
+      <c r="E4" s="79"/>
+      <c r="F4" s="79"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="80"/>
     </row>
     <row r="5" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="110" t="s">
         <v>70</v>
       </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="110"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="113"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="45"/>
@@ -1963,10 +1963,10 @@
       <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:8" s="3" customFormat="1" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="111" t="s">
+      <c r="A10" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="112"/>
+      <c r="B10" s="115"/>
       <c r="C10" s="26">
         <f>'Bảng tính CK'!E14</f>
         <v>1476000</v>
@@ -1978,10 +1978,10 @@
       <c r="H10" s="32"/>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="97" t="s">
+      <c r="A11" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="98"/>
+      <c r="B11" s="104"/>
       <c r="C11" s="26">
         <v>3</v>
       </c>
@@ -1992,10 +1992,10 @@
       <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="113" t="s">
+      <c r="A12" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="114"/>
+      <c r="B12" s="117"/>
       <c r="C12" s="24">
         <v>0</v>
       </c>
@@ -2006,10 +2006,10 @@
       <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="102" t="s">
+      <c r="A13" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="103"/>
+      <c r="B13" s="106"/>
       <c r="C13" s="24">
         <f>COUNTIFS(C16:C19, "&gt;=2.5",C16:C19,"&lt;7")</f>
         <v>0</v>
@@ -2141,11 +2141,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="99" t="s">
+      <c r="A19" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="100"/>
-      <c r="C19" s="101"/>
+      <c r="B19" s="98"/>
+      <c r="C19" s="99"/>
       <c r="D19" s="54">
         <f>SUM(D16:D18)</f>
         <v>3</v>
@@ -2156,11 +2156,11 @@
       <c r="H19" s="26"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="118"/>
-      <c r="C20" s="77"/>
+      <c r="B20" s="100"/>
+      <c r="C20" s="93"/>
       <c r="D20" s="19"/>
       <c r="E20" s="27">
         <f>SUM(E16:E18)</f>
@@ -2203,40 +2203,40 @@
       <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="79" t="s">
+      <c r="A23" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79" t="s">
+      <c r="B23" s="95"/>
+      <c r="C23" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="119" t="s">
+      <c r="D23" s="95"/>
+      <c r="E23" s="101" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="119"/>
-      <c r="G23" s="79" t="s">
+      <c r="F23" s="101"/>
+      <c r="G23" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="H23" s="79"/>
+      <c r="H23" s="95"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="80" t="s">
+      <c r="A24" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="B24" s="80"/>
-      <c r="C24" s="80" t="s">
+      <c r="B24" s="96"/>
+      <c r="C24" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="80"/>
-      <c r="E24" s="120" t="s">
+      <c r="D24" s="96"/>
+      <c r="E24" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="120"/>
-      <c r="G24" s="80" t="s">
+      <c r="F24" s="102"/>
+      <c r="G24" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="H24" s="80"/>
+      <c r="H24" s="96"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="31"/>
@@ -2279,25 +2279,35 @@
       <c r="H28" s="32"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="79" t="s">
+      <c r="A29" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="B29" s="79"/>
-      <c r="C29" s="79" t="s">
+      <c r="B29" s="95"/>
+      <c r="C29" s="95" t="s">
         <v>5</v>
       </c>
-      <c r="D29" s="79"/>
-      <c r="E29" s="119" t="s">
+      <c r="D29" s="95"/>
+      <c r="E29" s="101" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="119"/>
-      <c r="G29" s="79" t="s">
+      <c r="F29" s="101"/>
+      <c r="G29" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="79"/>
+      <c r="H29" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B4"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C2:H2"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="A24:B24"/>
@@ -2312,16 +2322,6 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A1:B4"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <pageMargins left="0.9" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="91" orientation="landscape" horizontalDpi="203" verticalDpi="203" r:id="rId1"/>
@@ -2351,55 +2351,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="130"/>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="131" t="s">
+      <c r="A1" s="135"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="136" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="148" t="s">
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="142" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="149"/>
+      <c r="H1" s="143"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="130"/>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134"/>
-      <c r="G2" s="148" t="s">
+      <c r="A2" s="135"/>
+      <c r="B2" s="135"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="142" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="149"/>
+      <c r="H2" s="143"/>
     </row>
     <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="130"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="135"/>
-      <c r="E3" s="136"/>
-      <c r="F3" s="136"/>
-      <c r="G3" s="148" t="s">
+      <c r="A3" s="135"/>
+      <c r="B3" s="135"/>
+      <c r="C3" s="135"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="141"/>
+      <c r="F3" s="141"/>
+      <c r="G3" s="142" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="149"/>
+      <c r="H3" s="143"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="129" t="str">
+      <c r="A4" s="134" t="str">
         <f>'Phiếu tính CK'!H6</f>
         <v>Hà Nội, ngày 30 tháng 09 năm 2026</v>
       </c>
-      <c r="B4" s="129"/>
-      <c r="C4" s="129"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
+      <c r="B4" s="134"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
+      <c r="E4" s="134"/>
+      <c r="F4" s="134"/>
+      <c r="G4" s="134"/>
+      <c r="H4" s="134"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="64" t="s">
@@ -2436,27 +2436,27 @@
       <c r="H7" s="65"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="144" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="123" t="s">
+      <c r="B8" s="144" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="125" t="s">
+      <c r="C8" s="146" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-      <c r="F8" s="127"/>
-      <c r="G8" s="128" t="s">
+      <c r="D8" s="147"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="149" t="s">
         <v>45</v>
       </c>
-      <c r="H8" s="128"/>
+      <c r="H8" s="149"/>
       <c r="I8" s="30"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="124"/>
-      <c r="B9" s="124"/>
+      <c r="A9" s="145"/>
+      <c r="B9" s="145"/>
       <c r="C9" s="70" t="s">
         <v>59</v>
       </c>
@@ -2469,8 +2469,8 @@
       <c r="F9" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
+      <c r="G9" s="149"/>
+      <c r="H9" s="149"/>
       <c r="I9" s="30"/>
     </row>
     <row r="10" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2595,10 +2595,10 @@
         <f>D14-E14</f>
         <v>2</v>
       </c>
-      <c r="G14" s="142" t="s">
+      <c r="G14" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="H14" s="142"/>
+      <c r="H14" s="126"/>
       <c r="I14" s="30"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -2621,10 +2621,10 @@
         <f t="shared" ref="F15" si="0">D15</f>
         <v>178</v>
       </c>
-      <c r="G15" s="142" t="s">
+      <c r="G15" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="H15" s="142"/>
+      <c r="H15" s="126"/>
       <c r="I15" s="30"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -2647,10 +2647,10 @@
         <f>D16-E16</f>
         <v>52</v>
       </c>
-      <c r="G16" s="142" t="s">
+      <c r="G16" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="H16" s="142"/>
+      <c r="H16" s="126"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
@@ -2672,10 +2672,10 @@
         <f>D17-E17</f>
         <v>22</v>
       </c>
-      <c r="G17" s="142" t="s">
+      <c r="G17" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="H17" s="142"/>
+      <c r="H17" s="126"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="51">
@@ -2697,10 +2697,10 @@
         <f>D18-E18</f>
         <v>2</v>
       </c>
-      <c r="G18" s="142" t="s">
+      <c r="G18" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="H18" s="142"/>
+      <c r="H18" s="126"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="51">
@@ -2721,10 +2721,10 @@
       <c r="F19" s="23">
         <v>3</v>
       </c>
-      <c r="G19" s="142" t="s">
+      <c r="G19" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="H19" s="142"/>
+      <c r="H19" s="126"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="51">
@@ -2744,10 +2744,10 @@
         <f>SUM(D20-E20)</f>
         <v>58</v>
       </c>
-      <c r="G20" s="143" t="s">
+      <c r="G20" s="132" t="s">
         <v>66</v>
       </c>
-      <c r="H20" s="144"/>
+      <c r="H20" s="133"/>
     </row>
     <row r="21" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="51">
@@ -2769,16 +2769,16 @@
         <f>SUM(D21-E21)</f>
         <v>1</v>
       </c>
-      <c r="G21" s="141" t="s">
+      <c r="G21" s="131" t="s">
         <v>74</v>
       </c>
-      <c r="H21" s="141"/>
+      <c r="H21" s="131"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="137" t="s">
+      <c r="A22" s="127" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="138"/>
+      <c r="B22" s="128"/>
       <c r="C22" s="52">
         <f>SUM(C10:C21)</f>
         <v>7160</v>
@@ -2795,8 +2795,8 @@
         <f>SUM(F10:F21)</f>
         <v>3331</v>
       </c>
-      <c r="G22" s="139"/>
-      <c r="H22" s="140"/>
+      <c r="G22" s="129"/>
+      <c r="H22" s="130"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="65"/>
@@ -2809,40 +2809,40 @@
       <c r="H23" s="65"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="147" t="s">
+      <c r="A24" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="147"/>
-      <c r="C24" s="147" t="s">
+      <c r="B24" s="125"/>
+      <c r="C24" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="147"/>
-      <c r="E24" s="147" t="s">
+      <c r="D24" s="125"/>
+      <c r="E24" s="125" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="147"/>
-      <c r="G24" s="79" t="s">
+      <c r="F24" s="125"/>
+      <c r="G24" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="H24" s="79"/>
+      <c r="H24" s="95"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="146" t="s">
+      <c r="A25" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="146"/>
-      <c r="C25" s="146" t="s">
+      <c r="B25" s="124"/>
+      <c r="C25" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="D25" s="146"/>
-      <c r="E25" s="146" t="s">
+      <c r="D25" s="124"/>
+      <c r="E25" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="146"/>
-      <c r="G25" s="146" t="s">
+      <c r="F25" s="124"/>
+      <c r="G25" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="H25" s="146"/>
+      <c r="H25" s="124"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="71"/>
@@ -2885,22 +2885,22 @@
       <c r="H29" s="73"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="145" t="s">
+      <c r="A30" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="145"/>
-      <c r="C30" s="145" t="s">
+      <c r="B30" s="123"/>
+      <c r="C30" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="D30" s="145"/>
-      <c r="E30" s="145" t="s">
+      <c r="D30" s="123"/>
+      <c r="E30" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="145"/>
-      <c r="G30" s="145" t="s">
+      <c r="F30" s="123"/>
+      <c r="G30" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="H30" s="145"/>
+      <c r="H30" s="123"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="65"/>
@@ -2914,6 +2914,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="G8:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A1:C3"/>
+    <mergeCell ref="D1:F3"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="G20:H20"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="G12:H12"/>
@@ -2930,26 +2950,6 @@
     <mergeCell ref="E24:F24"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="G14:H14"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A1:C3"/>
-    <mergeCell ref="D1:F3"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.5" right="1" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
